--- a/output/pdf_financials_xlsx/MPVD.xlsx
+++ b/output/pdf_financials_xlsx/MPVD.xlsx
@@ -6102,49 +6102,49 @@
         <v>1.238302</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.026302</v>
+        <v>1.238302</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.083422</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.233857</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.191406</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.507424</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.775687</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.018</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.549</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.111</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.469</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.552</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>9.866</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.138</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>11.626</v>
       </c>
     </row>
     <row r="93">
@@ -11388,7 +11388,11 @@
           <t>Share-based payments reserve 14</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12712,7 +12716,11 @@
           <t>Share-based payments reserve 12</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -16379,7 +16387,11 @@
           <t>Share-based payments reserve 13</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -17678,7 +17690,11 @@
           <t>Share‐based payments reserve 13</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -18686,7 +18702,11 @@
           <t>Share‐based payments reserve 12</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -22290,7 +22310,11 @@
           <t>Share‐based payments reserve 11</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -23397,7 +23421,11 @@
           <t>Share‐based payments reserve 10</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -25130,7 +25158,11 @@
           <t>Share-based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -26655,7 +26687,11 @@
           <t>Share-based payments reserve (Note 9) 1,083,422</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MPVD.xlsx
+++ b/output/pdf_financials_xlsx/MPVD.xlsx
@@ -1060,60 +1060,56 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.062155</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.036782</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.12259</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.303354</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.147762</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.355428</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.458659</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.130419</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.976039</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.582</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>1.372</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>2.627</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>2.663</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="13">
@@ -2109,49 +2105,49 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-14.534727</v>
+        <v>-14.657317</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-11.538935</v>
+        <v>-11.842289</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.33761</v>
+        <v>-3.485372</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-26.603938</v>
+        <v>-26.959366</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.394079</v>
+        <v>-4.852738</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-43.168971</v>
+        <v>-44.29939</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4.798</v>
+        <v>3.821961</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>17.152</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-20.082</v>
+        <v>-20.664</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-128.751</v>
+        <v>-129.272</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>296.887</v>
+        <v>296.685</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>70.395</v>
+        <v>69.023</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-44.871</v>
+        <v>-47.498</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-80.84099999999999</v>
+        <v>-83.504</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-279.693</v>
+        <v>-280.666</v>
       </c>
     </row>
     <row r="28">
@@ -2229,49 +2225,49 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-14.534727</v>
+        <v>-14.657317</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-11.538935</v>
+        <v>-11.842289</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.33761</v>
+        <v>-3.485372</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-26.603938</v>
+        <v>-26.959366</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.394079</v>
+        <v>-4.852738</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-43.168971</v>
+        <v>-44.29939</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>4.798</v>
+        <v>3.821961</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>17.152</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-20.082</v>
+        <v>-20.664</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-128.751</v>
+        <v>-129.272</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>296.887</v>
+        <v>296.685</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>70.395</v>
+        <v>69.023</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-44.871</v>
+        <v>-47.498</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-80.84099999999999</v>
+        <v>-83.504</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-279.693</v>
+        <v>-280.666</v>
       </c>
     </row>
     <row r="30">
@@ -2331,25 +2327,25 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-6.457878438043664</v>
+        <v>-6.645035357222103</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-46.59252933044794</v>
+        <v>-46.78106928571945</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>96.16614246428028</v>
+        <v>96.10071164117996</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>18.10324209919944</v>
+        <v>17.75040953779449</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-13.65395733803974</v>
+        <v>-14.45333657913154</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-30.20230512020623</v>
+        <v>-31.19720546205145</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-179.6069995183818</v>
+        <v>-180.2318189115428</v>
       </c>
     </row>
     <row r="31">
@@ -2523,40 +2519,40 @@
         <v>0.274696</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>11.344472</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.779907</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>9.081791000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.844</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>43.129</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>30.708</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>34.751</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>17.247</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>29.674</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>11.561</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.327</v>
       </c>
     </row>
     <row r="35">
@@ -2643,40 +2639,40 @@
         <v>47.693693</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>24.343222</v>
+        <v>35.687694</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>77.261842</v>
+        <v>81.041749</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>9.081791000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.844</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>43.129</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>30.708</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>34.751</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>17.247</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>29.674</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>11.561</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.327</v>
       </c>
     </row>
     <row r="37">
@@ -3363,7 +3359,7 @@
         <v>0.731923</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>24.124887</v>
+        <v>12.780415</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -3372,31 +3368,31 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.162000000000001</v>
+        <v>1.318</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>46.593</v>
+        <v>3.464</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>31.977</v>
+        <v>1.269</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>26.914</v>
+        <v>1.914</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>19.806</v>
+        <v>2.559</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>45.093</v>
+        <v>15.419</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>18.41</v>
+        <v>6.849</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.055</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="49">
@@ -9175,7 +9171,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9820,7 +9816,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -16886,7 +16886,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -22415,7 +22419,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -28624,7 +28628,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -46482,7 +46486,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -47676,7 +47680,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -47773,7 +47777,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -48573,7 +48577,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -50868,7 +50872,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -53068,7 +53072,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -53270,7 +53274,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -54583,7 +54587,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -54686,7 +54690,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -54987,7 +54991,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -55189,7 +55193,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -56500,7 +56504,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -56603,7 +56607,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -57935,7 +57939,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -58644,7 +58648,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -59230,7 +59234,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -64602,7 +64606,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -66309,7 +66313,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E576" s="5" t="n">

--- a/output/pdf_financials_xlsx/MPVD.xlsx
+++ b/output/pdf_financials_xlsx/MPVD.xlsx
@@ -1153,16 +1153,16 @@
         <v>-0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>40.564</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>38.637</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>40.373</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>46.44</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>-0</v>
@@ -2129,16 +2129,16 @@
         <v>17.152</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-20.664</v>
+        <v>-61.228</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-129.272</v>
+        <v>-167.909</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>296.685</v>
+        <v>256.312</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>69.023</v>
+        <v>22.583</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-47.498</v>
@@ -2249,16 +2249,16 @@
         <v>17.152</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-20.664</v>
+        <v>-61.228</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-129.272</v>
+        <v>-167.909</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>296.685</v>
+        <v>256.312</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>69.023</v>
+        <v>22.583</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-47.498</v>
@@ -2327,16 +2327,16 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-6.645035357222103</v>
+        <v>-19.68942241831179</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-46.78106928571945</v>
+        <v>-60.76306209152692</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>96.10071164117996</v>
+        <v>83.02329272519378</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>17.75040953779449</v>
+        <v>5.807593100734725</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-14.45333657913154</v>
@@ -51769,7 +51769,11 @@
           <t>Net finance expenses 12</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MPVD.xlsx
+++ b/output/pdf_financials_xlsx/MPVD.xlsx
@@ -764,19 +764,19 @@
         <v>1.242122</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.894469</v>
+        <v>0.992281</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.928809</v>
+        <v>1.095477</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7762250000000001</v>
+        <v>0.921378</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.897439</v>
+        <v>1.161671</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.383829</v>
+        <v>1.563507</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>6.277</v>
@@ -950,19 +950,19 @@
         <v>1.287284</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.992281</v>
+        <v>1.090093</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.095477</v>
+        <v>1.262145</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.7762250000000001</v>
+        <v>0.921378</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.897439</v>
+        <v>1.161671</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.383829</v>
+        <v>1.563507</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>6.277</v>
@@ -1012,19 +1012,19 @@
         <v>-1.287284</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.992281</v>
+        <v>-1.090093</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.095477</v>
+        <v>-1.262145</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.7762250000000001</v>
+        <v>-0.921378</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.897439</v>
+        <v>-1.161671</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.383829</v>
+        <v>-1.563507</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-6.277</v>
@@ -1033,10 +1033,10 @@
         <v>36.068</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>270.405</v>
+        <v>81.03100000000001</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>237.697</v>
+        <v>24.843</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>334.916</v>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-14.534727</v>
+        <v>-14.025041</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-11.538935</v>
@@ -1366,18 +1366,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0.222166</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0.222796</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.509686</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2105,7 +2101,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-14.657317</v>
+        <v>-14.147631</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-11.842289</v>
@@ -2225,7 +2221,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-14.657317</v>
+        <v>-14.147631</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-11.842289</v>
@@ -2365,7 +2361,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.63411415339178</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -4744,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.317</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="71">
@@ -4804,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>61.231</v>
+        <v>61.548</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>73.374</v>
+        <v>73.548</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>92.286</v>
+        <v>92.509</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>161.586</v>
+        <v>161.839</v>
       </c>
     </row>
     <row r="72">
@@ -5044,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>376.421</v>
+        <v>376.238</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
@@ -5053,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>179.04</v>
+        <v>178.817</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5383,22 +5379,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" s="3" t="n">
+        <v>0.0005217614438251102</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.150386336508186</v>
+        <v>0.1511649040421655</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.2032498254866982</v>
+        <v>0.2037318146059323</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.3284608403181891</v>
+        <v>0.3292545334828181</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>36.39324324324324</v>
+        <v>36.45022522522522</v>
       </c>
     </row>
     <row r="81">
@@ -7039,31 +7033,31 @@
         </is>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>1.582</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>1.685</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>1.923</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>1.363</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.794</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="108">
@@ -10796,7 +10790,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -31365,7 +31363,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -37611,7 +37613,11 @@
           <t>Share‐based payment expense</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -47179,7 +47185,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -49171,7 +49181,11 @@
           <t>Earnings from mine operations</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -57472,7 +57486,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -57489,22 +57507,22 @@
         </is>
       </c>
       <c r="H487" s="5" t="n">
-        <v>-0.097812</v>
+        <v>0.097812</v>
       </c>
       <c r="I487" s="5" t="n">
-        <v>-0.166668</v>
+        <v>0.166668</v>
       </c>
       <c r="J487" s="5" t="n">
-        <v>-0.145153</v>
+        <v>0.145153</v>
       </c>
       <c r="K487" s="5" t="n">
-        <v>-0.264232</v>
+        <v>0.264232</v>
       </c>
       <c r="L487" s="5" t="n">
-        <v>-0.179678</v>
+        <v>0.179678</v>
       </c>
       <c r="M487" s="5" t="n">
-        <v>-0.183898</v>
+        <v>0.183898</v>
       </c>
       <c r="N487" t="inlineStr">
         <is>
@@ -64711,7 +64729,11 @@
           <t>Future income tax recovery (Note 7) 498,745</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -66717,7 +66739,11 @@
           <t>Future income tax recovery (Note 7) 509,686</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E580" s="5" t="n">
         <v>0.222166</v>
       </c>
